--- a/estudiantes.xlsx
+++ b/estudiantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unisimonedu-my.sharepoint.com/personal/wilson_castellanosv_unisimon_edu_co/Documents/2026/Del Colegio a Unisimón/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{771BCFF8-DBAE-49BF-B750-E72196680869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{771BCFF8-DBAE-49BF-B750-E72196680869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34277333-AC32-48AF-B211-02C3EDCA369A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C6EF30D0-FF15-4CD4-92F1-E41695A57048}"/>
   </bookViews>
@@ -1808,9 +1808,6 @@
     <t>Colegio Gonzalo Rivera Laguado</t>
   </si>
   <si>
-    <t>Andres Bello</t>
-  </si>
-  <si>
     <t>Colegio Luis Carlos Galan Sarmiento</t>
   </si>
   <si>
@@ -1914,6 +1911,9 @@
   </si>
   <si>
     <t>TRABAJO SOCIAL</t>
+  </si>
+  <si>
+    <t>Colegio Andres Bello</t>
   </si>
 </sst>
 </file>
@@ -2389,7 +2389,7 @@
         <v>588</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2403,10 +2403,10 @@
         <v>1092534964</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2420,10 +2420,10 @@
         <v>1092537059</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2437,10 +2437,10 @@
         <v>1094052712</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2454,10 +2454,10 @@
         <v>1091979804</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2471,10 +2471,10 @@
         <v>1090437201</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2488,10 +2488,10 @@
         <v>1090385046</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2505,10 +2505,10 @@
         <v>1127658503</v>
       </c>
       <c r="D9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2522,10 +2522,10 @@
         <v>1092536878</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2539,10 +2539,10 @@
         <v>1092533900</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2556,10 +2556,10 @@
         <v>1094053556</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2576,7 +2576,7 @@
         <v>588</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2590,10 +2590,10 @@
         <v>1094053187</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2607,10 +2607,10 @@
         <v>1016041526</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2624,10 +2624,10 @@
         <v>1092945020</v>
       </c>
       <c r="D16" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E16" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2641,10 +2641,10 @@
         <v>1091980752</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2658,10 +2658,10 @@
         <v>1092537874</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2675,10 +2675,10 @@
         <v>1093301679</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2692,10 +2692,10 @@
         <v>1091981605</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2709,10 +2709,10 @@
         <v>1092946078</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2726,10 +2726,10 @@
         <v>1091361112</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>588</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2760,10 +2760,10 @@
         <v>7704788</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2777,10 +2777,10 @@
         <v>1094053211</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2794,10 +2794,10 @@
         <v>1094053910</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2811,10 +2811,10 @@
         <v>1149465567</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2828,10 +2828,10 @@
         <v>1093599144</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2845,10 +2845,10 @@
         <v>1126424650</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2862,10 +2862,10 @@
         <v>1091976025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2879,10 +2879,10 @@
         <v>1025064345</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2896,10 +2896,10 @@
         <v>1091360424</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2916,7 +2916,7 @@
         <v>588</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2930,10 +2930,10 @@
         <v>1092343207</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2947,10 +2947,10 @@
         <v>1092945404</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2964,10 +2964,10 @@
         <v>1092946542</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2981,10 +2981,10 @@
         <v>1091978791</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2998,10 +2998,10 @@
         <v>1091976275</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3015,10 +3015,10 @@
         <v>1092947541</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,10 @@
         <v>1090419598</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3049,10 +3049,10 @@
         <v>1127048335</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3066,10 +3066,10 @@
         <v>1092391604</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3083,10 +3083,10 @@
         <v>1093302640</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3100,10 +3100,10 @@
         <v>1148954319</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3117,10 +3117,10 @@
         <v>1127360258</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3134,10 +3134,10 @@
         <v>1094055804</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3151,10 +3151,10 @@
         <v>1093301194</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3168,10 +3168,10 @@
         <v>1094052227</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>1030040974</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3202,10 +3202,10 @@
         <v>1092535898</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3219,10 +3219,10 @@
         <v>1091974882</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3236,10 +3236,10 @@
         <v>1090423988</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3253,10 +3253,10 @@
         <v>1091982241</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3270,10 +3270,10 @@
         <v>1092536353</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3287,10 +3287,10 @@
         <v>1064796517</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3304,10 +3304,10 @@
         <v>1127051841</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3321,10 +3321,10 @@
         <v>1092537856</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3338,10 +3338,10 @@
         <v>1092946382</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3355,10 +3355,10 @@
         <v>1091361943</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3372,10 +3372,10 @@
         <v>106290086664</v>
       </c>
       <c r="D60" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3389,10 +3389,10 @@
         <v>1091979127</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3406,10 +3406,10 @@
         <v>1092947321</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3423,10 +3423,10 @@
         <v>1065646657</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3440,10 +3440,10 @@
         <v>1094447499</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3457,10 +3457,10 @@
         <v>1091361489</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3474,10 +3474,10 @@
         <v>1092946733</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3491,10 +3491,10 @@
         <v>1093598851</v>
       </c>
       <c r="D67" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E67" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -3508,10 +3508,10 @@
         <v>1090439005</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3525,10 +3525,10 @@
         <v>1076507828</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3542,10 +3542,10 @@
         <v>1094049337</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3559,10 +3559,10 @@
         <v>1093599248</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3576,10 +3576,10 @@
         <v>1093758488</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3593,10 +3593,10 @@
         <v>1091974878</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3610,10 +3610,10 @@
         <v>1110510788</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3627,10 +3627,10 @@
         <v>1091979213</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3644,10 +3644,10 @@
         <v>1093599162</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3661,10 +3661,10 @@
         <v>1093301646</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3678,10 +3678,10 @@
         <v>1232593939</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3695,10 +3695,10 @@
         <v>1094221476</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3712,10 +3712,10 @@
         <v>1093302031</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3729,10 +3729,10 @@
         <v>1091977878</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3746,10 +3746,10 @@
         <v>1091978811</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3763,10 +3763,10 @@
         <v>1093599780</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3780,10 +3780,10 @@
         <v>1092537114</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3797,10 +3797,10 @@
         <v>1093601080</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3814,10 +3814,10 @@
         <v>1094054137</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3831,10 +3831,10 @@
         <v>1091980194</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3848,10 +3848,10 @@
         <v>1092944759</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,10 +3865,10 @@
         <v>1093597850</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,10 +3882,10 @@
         <v>1029401766</v>
       </c>
       <c r="D90" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E90" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3899,10 +3899,10 @@
         <v>1093302625</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3916,10 +3916,10 @@
         <v>5707410</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3933,10 +3933,10 @@
         <v>1101340</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3950,10 +3950,10 @@
         <v>1090520248</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3967,10 +3967,10 @@
         <v>1090434380</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3984,10 +3984,10 @@
         <v>1093598240</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,10 +4001,10 @@
         <v>1093595681</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4018,10 +4018,10 @@
         <v>1127358758</v>
       </c>
       <c r="D98" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E98" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4035,10 +4035,10 @@
         <v>1090431969</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4052,10 +4052,10 @@
         <v>1092945716</v>
       </c>
       <c r="D100" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E100" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4069,10 +4069,10 @@
         <v>1092947356</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4086,10 +4086,10 @@
         <v>1090474286</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4103,10 +4103,10 @@
         <v>6152393</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4120,10 +4120,10 @@
         <v>1092388889</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4137,10 +4137,10 @@
         <v>1093300998</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4154,10 +4154,10 @@
         <v>1092946648</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4171,10 +4171,10 @@
         <v>1093600121</v>
       </c>
       <c r="D107" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E107" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4188,10 +4188,10 @@
         <v>1094048621</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4205,10 +4205,10 @@
         <v>1093600765</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -4222,10 +4222,10 @@
         <v>1092945259</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -4239,10 +4239,10 @@
         <v>1092944636</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -4256,10 +4256,10 @@
         <v>1091362509</v>
       </c>
       <c r="D112" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -4273,10 +4273,10 @@
         <v>1091979298</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -4290,10 +4290,10 @@
         <v>1142718239</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -4310,7 +4310,7 @@
         <v>588</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -4324,10 +4324,10 @@
         <v>1092943899</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -4341,10 +4341,10 @@
         <v>1090426265</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -4358,10 +4358,10 @@
         <v>5828829</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -4375,10 +4375,10 @@
         <v>1091981814</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -4395,7 +4395,7 @@
         <v>588</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -4409,10 +4409,10 @@
         <v>1092946814</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -4426,10 +4426,10 @@
         <v>1091362734</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -4443,10 +4443,10 @@
         <v>1034782466</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -4460,10 +4460,10 @@
         <v>1183713018</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -4477,10 +4477,10 @@
         <v>1093597863</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -4494,10 +4494,10 @@
         <v>1030060516</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -4511,10 +4511,10 @@
         <v>1091362280</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -4531,7 +4531,7 @@
         <v>588</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -4545,10 +4545,10 @@
         <v>1127345030</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -4562,10 +4562,10 @@
         <v>1094054384</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -4579,10 +4579,10 @@
         <v>1094222012</v>
       </c>
       <c r="D131" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -4596,10 +4596,10 @@
         <v>1093302655</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4613,10 +4613,10 @@
         <v>1093597855</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4630,10 +4630,10 @@
         <v>1094054415</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -4647,10 +4647,10 @@
         <v>1093297176</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -4664,10 +4664,10 @@
         <v>1093599932</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4681,10 +4681,10 @@
         <v>1091978969</v>
       </c>
       <c r="D137" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E137" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -4698,10 +4698,10 @@
         <v>1091976475</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -4715,10 +4715,10 @@
         <v>1091982486</v>
       </c>
       <c r="D139" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E139" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -4732,10 +4732,10 @@
         <v>1093599623</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4749,10 +4749,10 @@
         <v>1093298236</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4766,10 +4766,10 @@
         <v>1091981245</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4783,10 +4783,10 @@
         <v>1093598137</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -4800,10 +4800,10 @@
         <v>1093302496</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4817,10 +4817,10 @@
         <v>1090434688</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -4834,10 +4834,10 @@
         <v>7662866</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -4851,10 +4851,10 @@
         <v>1091979906</v>
       </c>
       <c r="D147" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E147" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>1092946823</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4885,10 +4885,10 @@
         <v>1092946173</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -4902,10 +4902,10 @@
         <v>5224194</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -4919,10 +4919,10 @@
         <v>1093596931</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -4936,10 +4936,10 @@
         <v>1090509327</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -4953,10 +4953,10 @@
         <v>1092537531</v>
       </c>
       <c r="D153" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E153" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -4970,10 +4970,10 @@
         <v>1093600000</v>
       </c>
       <c r="D154" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E154" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -4987,10 +4987,10 @@
         <v>1140416716</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -5004,10 +5004,10 @@
         <v>1091981126</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -5021,10 +5021,10 @@
         <v>1090440910</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -5038,10 +5038,10 @@
         <v>1102364552</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -5055,10 +5055,10 @@
         <v>1091981235</v>
       </c>
       <c r="D159" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E159" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5072,10 +5072,10 @@
         <v>1093413049</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -5089,10 +5089,10 @@
         <v>1092536055</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5106,10 +5106,10 @@
         <v>6770430</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -5123,10 +5123,10 @@
         <v>1091362054</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -5140,10 +5140,10 @@
         <v>1092535094</v>
       </c>
       <c r="D164" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E164" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5157,10 +5157,10 @@
         <v>1092537323</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -5174,10 +5174,10 @@
         <v>1091974088</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -5191,10 +5191,10 @@
         <v>1091978107</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -5208,10 +5208,10 @@
         <v>1093599957</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -5225,10 +5225,10 @@
         <v>1091974916</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -5242,10 +5242,10 @@
         <v>1094221786</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5259,10 +5259,10 @@
         <v>1091979182</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -5276,10 +5276,10 @@
         <v>1094055634</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -5293,10 +5293,10 @@
         <v>1091979479</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -5310,10 +5310,10 @@
         <v>1020765009</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -5327,10 +5327,10 @@
         <v>1127051197</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -5344,10 +5344,10 @@
         <v>1094054203</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -5361,10 +5361,10 @@
         <v>5526781</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -5378,10 +5378,10 @@
         <v>1092946933</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5395,10 +5395,10 @@
         <v>5246648</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -5412,10 +5412,10 @@
         <v>1050611216</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>1127053174</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -5446,10 +5446,10 @@
         <v>1092537457</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -5463,10 +5463,10 @@
         <v>1091362218</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -5480,10 +5480,10 @@
         <v>1148217186</v>
       </c>
       <c r="D184" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E184" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -5497,10 +5497,10 @@
         <v>1093760</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -5514,10 +5514,10 @@
         <v>1245279053</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -5531,10 +5531,10 @@
         <v>1092945960</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -5548,10 +5548,10 @@
         <v>1094055408</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -5565,10 +5565,10 @@
         <v>1093302064</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -5582,10 +5582,10 @@
         <v>1092536311</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -5599,10 +5599,10 @@
         <v>1094348521</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -5616,10 +5616,10 @@
         <v>1092944323</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -5633,10 +5633,10 @@
         <v>1092945278</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -5650,10 +5650,10 @@
         <v>5792510</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -5667,10 +5667,10 @@
         <v>1062908635</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -5684,10 +5684,10 @@
         <v>1091979775</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -5701,10 +5701,10 @@
         <v>1091980267</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -5718,10 +5718,10 @@
         <v>1127355375</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -5735,10 +5735,10 @@
         <v>1091979076</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -5752,10 +5752,10 @@
         <v>1091983269</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -5769,10 +5769,10 @@
         <v>1092534996</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -5786,10 +5786,10 @@
         <v>1093301225</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -5803,10 +5803,10 @@
         <v>1093758076</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -5820,10 +5820,10 @@
         <v>1091979593</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -5837,10 +5837,10 @@
         <v>1091363313</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -5854,10 +5854,10 @@
         <v>1090508661</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -5871,10 +5871,10 @@
         <v>1092946650</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -5888,10 +5888,10 @@
         <v>6500648</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -5905,10 +5905,10 @@
         <v>1092538509</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -5922,10 +5922,10 @@
         <v>1093599971</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -5939,10 +5939,10 @@
         <v>6815964</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -5956,10 +5956,10 @@
         <v>1093752957</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -5973,10 +5973,10 @@
         <v>1092538360</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -5990,10 +5990,10 @@
         <v>1091361089</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6007,10 +6007,10 @@
         <v>1092947029</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6024,10 +6024,10 @@
         <v>1092945090</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6041,10 +6041,10 @@
         <v>1092945580</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -6058,10 +6058,10 @@
         <v>1090437625</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6075,10 +6075,10 @@
         <v>1092342112</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -6092,10 +6092,10 @@
         <v>1093753481</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6109,10 +6109,10 @@
         <v>1093600075</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6126,10 +6126,10 @@
         <v>1093598305</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6143,10 +6143,10 @@
         <v>1091980247</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6160,10 +6160,10 @@
         <v>1091361816</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6177,10 +6177,10 @@
         <v>1092537992</v>
       </c>
       <c r="D225" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E225" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6194,10 +6194,10 @@
         <v>1093301978</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6211,10 +6211,10 @@
         <v>1127946847</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6228,10 +6228,10 @@
         <v>1092535557</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6245,10 +6245,10 @@
         <v>1092536203</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6262,10 +6262,10 @@
         <v>1127050851</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6279,10 +6279,10 @@
         <v>1082606446</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6296,10 +6296,10 @@
         <v>1094054318</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -6313,10 +6313,10 @@
         <v>1127357671</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6330,10 +6330,10 @@
         <v>1091974909</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6347,10 +6347,10 @@
         <v>1091979846</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -6364,10 +6364,10 @@
         <v>1091978085</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -6381,10 +6381,10 @@
         <v>1014873678</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -6401,7 +6401,7 @@
         <v>588</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -6415,10 +6415,10 @@
         <v>1093302270</v>
       </c>
       <c r="D239" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E239" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,10 +6432,10 @@
         <v>1140421305</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -6449,10 +6449,10 @@
         <v>1094054962</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -6466,10 +6466,10 @@
         <v>1125759472</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -6483,10 +6483,10 @@
         <v>1091980774</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -6500,10 +6500,10 @@
         <v>1092946963</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -6517,10 +6517,10 @@
         <v>1094053893</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6534,10 +6534,10 @@
         <v>1094055412</v>
       </c>
       <c r="D246" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E246" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6551,10 +6551,10 @@
         <v>1090414848</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6571,7 +6571,7 @@
         <v>588</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -6585,10 +6585,10 @@
         <v>1091978761</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6602,10 +6602,10 @@
         <v>1091975746</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6619,10 +6619,10 @@
         <v>1091979536</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6636,10 +6636,10 @@
         <v>1127945554</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -6653,10 +6653,10 @@
         <v>1148954130</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -6670,10 +6670,10 @@
         <v>1093615171</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -6687,10 +6687,10 @@
         <v>1093300387</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6704,10 +6704,10 @@
         <v>1092533137</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6721,10 +6721,10 @@
         <v>1093802082</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -6738,10 +6738,10 @@
         <v>1093598785</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -6755,10 +6755,10 @@
         <v>5464247</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -6772,10 +6772,10 @@
         <v>1092966144</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -6789,10 +6789,10 @@
         <v>1091979801</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
@@ -6806,10 +6806,10 @@
         <v>1256319</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -6823,10 +6823,10 @@
         <v>1093299754</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
@@ -6840,10 +6840,10 @@
         <v>1018441201</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -6857,10 +6857,10 @@
         <v>1093762955</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -6874,10 +6874,10 @@
         <v>1091812275</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
@@ -6891,10 +6891,10 @@
         <v>1091362613</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -6908,10 +6908,10 @@
         <v>1030060285</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -6925,10 +6925,10 @@
         <v>1091362761</v>
       </c>
       <c r="D269" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E269" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -6942,10 +6942,10 @@
         <v>1092946384</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
@@ -6959,10 +6959,10 @@
         <v>1137719</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -6976,10 +6976,10 @@
         <v>1127595940</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -6993,10 +6993,10 @@
         <v>1093598072</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -7010,10 +7010,10 @@
         <v>1091978513</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -7027,10 +7027,10 @@
         <v>1092943381</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7044,10 +7044,10 @@
         <v>1091980894</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7061,10 +7061,10 @@
         <v>1092946012</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -7078,10 +7078,10 @@
         <v>1127347407</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -7095,10 +7095,10 @@
         <v>1094222262</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -7112,10 +7112,10 @@
         <v>1091978854</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -7129,10 +7129,10 @@
         <v>1094055100</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7146,10 +7146,10 @@
         <v>1091980466</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -7163,10 +7163,10 @@
         <v>1092946757</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7180,10 +7180,10 @@
         <v>1093309324</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -7197,10 +7197,10 @@
         <v>1091361992</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
@@ -7214,10 +7214,10 @@
         <v>1090449413</v>
       </c>
       <c r="D286" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E286" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7231,10 +7231,10 @@
         <v>1092947203</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -7248,10 +7248,10 @@
         <v>1092538716</v>
       </c>
       <c r="D288" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E288" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -7265,10 +7265,10 @@
         <v>1094054354</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -7282,10 +7282,10 @@
         <v>1094051540</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -7299,10 +7299,10 @@
         <v>1090393154</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -7316,10 +7316,10 @@
         <v>1093599762</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7333,10 +7333,10 @@
         <v>1094051887</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -7350,10 +7350,10 @@
         <v>1094053741</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7367,10 +7367,10 @@
         <v>1092944542</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -7384,10 +7384,10 @@
         <v>1030242123</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -7401,10 +7401,10 @@
         <v>1092947750</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7418,10 +7418,10 @@
         <v>7387500</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -7435,10 +7435,10 @@
         <v>2385584</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -7452,10 +7452,10 @@
         <v>1091978076</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -7469,10 +7469,10 @@
         <v>1093600914</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -7486,10 +7486,10 @@
         <v>1091979862</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -7503,10 +7503,10 @@
         <v>1091981621</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7520,10 +7520,10 @@
         <v>1091977941</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -7537,10 +7537,10 @@
         <v>1030060353</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
@@ -7554,10 +7554,10 @@
         <v>1090440918</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -7571,10 +7571,10 @@
         <v>1091979331</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
@@ -7588,10 +7588,10 @@
         <v>1043677227</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -7605,10 +7605,10 @@
         <v>1148704495</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -7622,10 +7622,10 @@
         <v>1096952785</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
@@ -7639,10 +7639,10 @@
         <v>1092537741</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -7656,10 +7656,10 @@
         <v>1091980704</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -7673,10 +7673,10 @@
         <v>1091982629</v>
       </c>
       <c r="D313" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
@@ -7690,10 +7690,10 @@
         <v>1091973415</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
@@ -7710,7 +7710,7 @@
         <v>588</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
@@ -7724,10 +7724,10 @@
         <v>1092538150</v>
       </c>
       <c r="D316" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
@@ -7741,10 +7741,10 @@
         <v>1091391579</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
@@ -7758,10 +7758,10 @@
         <v>1090456843</v>
       </c>
       <c r="D318" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E318" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
@@ -7775,10 +7775,10 @@
         <v>1091361794</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
@@ -7792,10 +7792,10 @@
         <v>1093413084</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
@@ -7809,10 +7809,10 @@
         <v>1094051318</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
@@ -7826,10 +7826,10 @@
         <v>1090450898</v>
       </c>
       <c r="D322" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E322" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
@@ -7843,10 +7843,10 @@
         <v>1030060502</v>
       </c>
       <c r="D323" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E323" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
@@ -7860,10 +7860,10 @@
         <v>1094055185</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -7877,10 +7877,10 @@
         <v>1091980319</v>
       </c>
       <c r="D325" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E325" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -7894,10 +7894,10 @@
         <v>1092538419</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
@@ -7911,10 +7911,10 @@
         <v>1092945955</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -7928,10 +7928,10 @@
         <v>1091982483</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -7948,7 +7948,7 @@
         <v>588</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -7962,10 +7962,10 @@
         <v>1093596535</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -7979,10 +7979,10 @@
         <v>1093597157</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -7999,7 +7999,7 @@
         <v>588</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -8013,10 +8013,10 @@
         <v>1092535598</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8030,10 +8030,10 @@
         <v>1091980526</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
@@ -8047,10 +8047,10 @@
         <v>1093301974</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
@@ -8064,10 +8064,10 @@
         <v>1092386675</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8081,10 +8081,10 @@
         <v>1091978746</v>
       </c>
       <c r="D337" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E337" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -8098,10 +8098,10 @@
         <v>1093301950</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8115,10 +8115,10 @@
         <v>1092388640</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
@@ -8132,10 +8132,10 @@
         <v>1090437202</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
@@ -8149,10 +8149,10 @@
         <v>1093758259</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -8166,10 +8166,10 @@
         <v>1090426977</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
@@ -8183,10 +8183,10 @@
         <v>1095839753</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
@@ -8200,10 +8200,10 @@
         <v>1093599888</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
@@ -8217,10 +8217,10 @@
         <v>1091362486</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -8237,7 +8237,7 @@
         <v>588</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -8251,10 +8251,10 @@
         <v>1091361366</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -8268,10 +8268,10 @@
         <v>1091979718</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
@@ -8285,10 +8285,10 @@
         <v>1094054112</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
@@ -8302,10 +8302,10 @@
         <v>1093594948</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8319,10 +8319,10 @@
         <v>1092537274</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8336,10 +8336,10 @@
         <v>1094055942</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -8356,7 +8356,7 @@
         <v>588</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -8373,7 +8373,7 @@
         <v>588</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8390,7 +8390,7 @@
         <v>588</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -8404,10 +8404,10 @@
         <v>1092946417</v>
       </c>
       <c r="D356" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
@@ -8421,10 +8421,10 @@
         <v>1092538132</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -8438,10 +8438,10 @@
         <v>1091977851</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8455,10 +8455,10 @@
         <v>1091362123</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -8472,10 +8472,10 @@
         <v>1092537381</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
@@ -8489,10 +8489,10 @@
         <v>1091978266</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
@@ -8506,10 +8506,10 @@
         <v>1092536465</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8523,10 +8523,10 @@
         <v>1148704011</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
@@ -8540,10 +8540,10 @@
         <v>1092946985</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
@@ -8557,10 +8557,10 @@
         <v>1127347347</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8577,7 +8577,7 @@
         <v>588</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -8591,10 +8591,10 @@
         <v>1094053345</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -8608,10 +8608,10 @@
         <v>1090434738</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -8625,10 +8625,10 @@
         <v>1093301726</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -8642,10 +8642,10 @@
         <v>1091979843</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8659,10 +8659,10 @@
         <v>1091361246</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -8676,10 +8676,10 @@
         <v>1128225578</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -8693,10 +8693,10 @@
         <v>1093599432</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -8710,10 +8710,10 @@
         <v>1093599768</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8727,10 +8727,10 @@
         <v>5892051</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8744,10 +8744,10 @@
         <v>1091980458</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -8761,10 +8761,10 @@
         <v>1091979100</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -8778,10 +8778,10 @@
         <v>1093300731</v>
       </c>
       <c r="D378" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
@@ -8795,10 +8795,10 @@
         <v>6290709</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -8812,10 +8812,10 @@
         <v>1091975808</v>
       </c>
       <c r="D380" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -8829,10 +8829,10 @@
         <v>1092947779</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -8846,10 +8846,10 @@
         <v>1092953076</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -8863,10 +8863,10 @@
         <v>1094054708</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
@@ -8880,10 +8880,10 @@
         <v>1092946710</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
@@ -8897,10 +8897,10 @@
         <v>1091979886</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -8914,10 +8914,10 @@
         <v>1093302431</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -8931,10 +8931,10 @@
         <v>1092947345</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -8948,10 +8948,10 @@
         <v>1091976732</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -8965,10 +8965,10 @@
         <v>1127658521</v>
       </c>
       <c r="D389" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E389" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -8982,10 +8982,10 @@
         <v>1092534869</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -8999,10 +8999,10 @@
         <v>1092945615</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
@@ -9016,10 +9016,10 @@
         <v>1094049486</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -9033,10 +9033,10 @@
         <v>1149457743</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
@@ -9050,10 +9050,10 @@
         <v>1127065536</v>
       </c>
       <c r="D394" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -9067,10 +9067,10 @@
         <v>1093598992</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
@@ -9084,10 +9084,10 @@
         <v>1094367168</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -9101,10 +9101,10 @@
         <v>1092536345</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -9118,10 +9118,10 @@
         <v>1090425527</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
@@ -9135,10 +9135,10 @@
         <v>1092536717</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
@@ -9152,10 +9152,10 @@
         <v>1127049056</v>
       </c>
       <c r="D400" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E400" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
@@ -9169,10 +9169,10 @@
         <v>1091360739</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -9186,10 +9186,10 @@
         <v>1189963133</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
@@ -9203,10 +9203,10 @@
         <v>1030060548</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -9220,10 +9220,10 @@
         <v>1092946545</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
@@ -9237,10 +9237,10 @@
         <v>5350012</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
@@ -9254,10 +9254,10 @@
         <v>1092538472</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
@@ -9271,10 +9271,10 @@
         <v>1091981708</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
@@ -9288,10 +9288,10 @@
         <v>1092945315</v>
       </c>
       <c r="D408" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E408" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
@@ -9305,10 +9305,10 @@
         <v>1148954031</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
@@ -9322,10 +9322,10 @@
         <v>1091976045</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
@@ -9339,10 +9339,10 @@
         <v>1049027222</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
@@ -9356,10 +9356,10 @@
         <v>1091360840</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -9373,10 +9373,10 @@
         <v>1091979496</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -9390,10 +9390,10 @@
         <v>5251399</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
@@ -9407,10 +9407,10 @@
         <v>1090962777</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
@@ -9424,10 +9424,10 @@
         <v>1091979210</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -9441,10 +9441,10 @@
         <v>1093434411</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -9458,10 +9458,10 @@
         <v>1091978861</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -9475,10 +9475,10 @@
         <v>1091980875</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -9492,10 +9492,10 @@
         <v>1094050953</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -9509,10 +9509,10 @@
         <v>1091974927</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -9529,7 +9529,7 @@
         <v>588</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
@@ -9543,10 +9543,10 @@
         <v>1090537705</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -9560,10 +9560,10 @@
         <v>1127049539</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
@@ -9580,7 +9580,7 @@
         <v>588</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
@@ -9594,10 +9594,10 @@
         <v>1094860586</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
@@ -9611,10 +9611,10 @@
         <v>1094053961</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
         <v>588</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
@@ -9645,10 +9645,10 @@
         <v>1092946702</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
@@ -9662,10 +9662,10 @@
         <v>1091998320</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
@@ -9679,10 +9679,10 @@
         <v>1091980083</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
@@ -9696,10 +9696,10 @@
         <v>1093764881</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
@@ -9713,10 +9713,10 @@
         <v>1090433375</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
@@ -9730,10 +9730,10 @@
         <v>1127049000</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
@@ -9747,10 +9747,10 @@
         <v>1093597548</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -9764,10 +9764,10 @@
         <v>1093301671</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -9781,10 +9781,10 @@
         <v>1091979734</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
@@ -9798,10 +9798,10 @@
         <v>1091974658</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
@@ -9815,10 +9815,10 @@
         <v>1092947488</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
@@ -9832,10 +9832,10 @@
         <v>1091362929</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
@@ -9849,10 +9849,10 @@
         <v>1094054233</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
@@ -9869,7 +9869,7 @@
         <v>588</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
@@ -9883,10 +9883,10 @@
         <v>1093301141</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
@@ -9900,10 +9900,10 @@
         <v>3170910390</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
@@ -9917,10 +9917,10 @@
         <v>1092537308</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
@@ -9934,10 +9934,10 @@
         <v>1091976004</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
@@ -9951,10 +9951,10 @@
         <v>1093301562</v>
       </c>
       <c r="D447" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -9968,10 +9968,10 @@
         <v>1091361827</v>
       </c>
       <c r="D448" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -9985,10 +9985,10 @@
         <v>1090435816</v>
       </c>
       <c r="D449" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E449" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
@@ -10002,10 +10002,10 @@
         <v>1091361484</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -10019,10 +10019,10 @@
         <v>1091980700</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -10036,10 +10036,10 @@
         <v>1091978598</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -10053,10 +10053,10 @@
         <v>1092947190</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
@@ -10070,10 +10070,10 @@
         <v>1091979808</v>
       </c>
       <c r="D454" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -10087,10 +10087,10 @@
         <v>1092538041</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -10104,10 +10104,10 @@
         <v>1092945903</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
@@ -10121,10 +10121,10 @@
         <v>1091359878</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -10138,10 +10138,10 @@
         <v>1092536773</v>
       </c>
       <c r="D458" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E458" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
@@ -10155,10 +10155,10 @@
         <v>1092534739</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
@@ -10172,10 +10172,10 @@
         <v>1030060250</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
@@ -10189,10 +10189,10 @@
         <v>1093763001</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
@@ -10206,10 +10206,10 @@
         <v>5227773</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
@@ -10226,7 +10226,7 @@
         <v>588</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
@@ -10240,10 +10240,10 @@
         <v>1092944562</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -10257,10 +10257,10 @@
         <v>1091977883</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
@@ -10274,10 +10274,10 @@
         <v>1094053614</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -10291,10 +10291,10 @@
         <v>1093911533</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -10308,10 +10308,10 @@
         <v>1096953725</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
@@ -10325,10 +10325,10 @@
         <v>1091980516</v>
       </c>
       <c r="D469" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E469" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
@@ -10342,10 +10342,10 @@
         <v>1092537559</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -10359,10 +10359,10 @@
         <v>1094268662</v>
       </c>
       <c r="D471" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -10376,10 +10376,10 @@
         <v>1094054074</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
@@ -10393,10 +10393,10 @@
         <v>1091978337</v>
       </c>
       <c r="D473" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -10410,10 +10410,10 @@
         <v>1094054993</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -10427,10 +10427,10 @@
         <v>1093761308</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10444,10 +10444,10 @@
         <v>1092944743</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
@@ -10464,7 +10464,7 @@
         <v>588</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
@@ -10478,10 +10478,10 @@
         <v>1091361907</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -10495,10 +10495,10 @@
         <v>1092947007</v>
       </c>
       <c r="D479" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -10512,10 +10512,10 @@
         <v>1093598245</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10529,10 +10529,10 @@
         <v>1091976754</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
@@ -10546,10 +10546,10 @@
         <v>1092947395</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
@@ -10563,10 +10563,10 @@
         <v>1148954433</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
@@ -10580,10 +10580,10 @@
         <v>1092001118</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
@@ -10597,10 +10597,10 @@
         <v>1127349468</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
@@ -10614,10 +10614,10 @@
         <v>1093303479</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
@@ -10631,10 +10631,10 @@
         <v>1093600800</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
@@ -10648,10 +10648,10 @@
         <v>1092945676</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
@@ -10665,10 +10665,10 @@
         <v>1096245629</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
@@ -10682,10 +10682,10 @@
         <v>1092180722</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
@@ -10699,10 +10699,10 @@
         <v>1094222000</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -10716,10 +10716,10 @@
         <v>1092945317</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
@@ -10733,10 +10733,10 @@
         <v>1096804424</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
@@ -10750,10 +10750,10 @@
         <v>1030060307</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
@@ -10767,10 +10767,10 @@
         <v>1093911369</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
@@ -10784,10 +10784,10 @@
         <v>1094053970</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
@@ -10801,10 +10801,10 @@
         <v>1091980919</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
@@ -10818,10 +10818,10 @@
         <v>1093598479</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
@@ -10835,10 +10835,10 @@
         <v>5107593</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
@@ -10852,10 +10852,10 @@
         <v>1091979602</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
@@ -10869,10 +10869,10 @@
         <v>1030041193</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
@@ -10886,10 +10886,10 @@
         <v>1092946181</v>
       </c>
       <c r="D502" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E502" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -10903,10 +10903,10 @@
         <v>1091979460</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
@@ -10920,10 +10920,10 @@
         <v>1090553680</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
@@ -10937,10 +10937,10 @@
         <v>1030060473</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -10954,10 +10954,10 @@
         <v>1091981186</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
@@ -10971,10 +10971,10 @@
         <v>1092945123</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
@@ -10988,10 +10988,10 @@
         <v>1020744905</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
@@ -11005,10 +11005,10 @@
         <v>1127347283</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
@@ -11022,10 +11022,10 @@
         <v>1013143334</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
@@ -11042,7 +11042,7 @@
         <v>588</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
@@ -11056,10 +11056,10 @@
         <v>1094055437</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
@@ -11073,10 +11073,10 @@
         <v>1094051566</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
@@ -11090,10 +11090,10 @@
         <v>1092536090</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
@@ -11107,10 +11107,10 @@
         <v>1094055491</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
@@ -11124,10 +11124,10 @@
         <v>7358047</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
@@ -11141,10 +11141,10 @@
         <v>1091361820</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
@@ -11158,10 +11158,10 @@
         <v>1093599602</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
@@ -11175,10 +11175,10 @@
         <v>1090441662</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
@@ -11192,10 +11192,10 @@
         <v>1092537060</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
@@ -11209,10 +11209,10 @@
         <v>1092946087</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
@@ -11226,10 +11226,10 @@
         <v>1091981768</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
@@ -11243,10 +11243,10 @@
         <v>1092943572</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E523" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
@@ -11260,10 +11260,10 @@
         <v>1092946550</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
@@ -11277,10 +11277,10 @@
         <v>1093300717</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
@@ -11294,10 +11294,10 @@
         <v>1093301806</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
@@ -11311,10 +11311,10 @@
         <v>1091979707</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -11328,10 +11328,10 @@
         <v>1091980057</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -11345,10 +11345,10 @@
         <v>1091806221</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E529" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
@@ -11365,7 +11365,7 @@
         <v>588</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -11379,10 +11379,10 @@
         <v>1090520483</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -11396,10 +11396,10 @@
         <v>1091979929</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -11413,10 +11413,10 @@
         <v>1030060343</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -11430,10 +11430,10 @@
         <v>1091977212</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -11450,7 +11450,7 @@
         <v>588</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
@@ -11467,7 +11467,7 @@
         <v>588</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
@@ -11481,10 +11481,10 @@
         <v>1094348247</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -11498,10 +11498,10 @@
         <v>1091978375</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
@@ -11515,10 +11515,10 @@
         <v>1093302426</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
@@ -11532,10 +11532,10 @@
         <v>1093599059</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11552,7 +11552,7 @@
         <v>588</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -11566,10 +11566,10 @@
         <v>1092536054</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -11583,10 +11583,10 @@
         <v>1091369028</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -11600,10 +11600,10 @@
         <v>1091978877</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -11617,10 +11617,10 @@
         <v>1044632426</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -11634,10 +11634,10 @@
         <v>1127057409</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
@@ -11651,10 +11651,10 @@
         <v>1091976301</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
@@ -11668,10 +11668,10 @@
         <v>1093301947</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
@@ -11685,10 +11685,10 @@
         <v>1093596673</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -11702,10 +11702,10 @@
         <v>1092943507</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
@@ -11719,10 +11719,10 @@
         <v>1091979559</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -11736,10 +11736,10 @@
         <v>1091361582</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
@@ -11753,10 +11753,10 @@
         <v>1091974981</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -11770,10 +11770,10 @@
         <v>1091362282</v>
       </c>
       <c r="D554" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E554" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
@@ -11787,10 +11787,10 @@
         <v>1090439668</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
@@ -11804,10 +11804,10 @@
         <v>1094053554</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11821,10 +11821,10 @@
         <v>1091975810</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11838,10 +11838,10 @@
         <v>1092537908</v>
       </c>
       <c r="D558" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E558" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
@@ -11855,10 +11855,10 @@
         <v>1090449366</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
@@ -11872,10 +11872,10 @@
         <v>1157963048</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -11889,10 +11889,10 @@
         <v>1064996939</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
@@ -11906,10 +11906,10 @@
         <v>1093413083</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
@@ -11923,10 +11923,10 @@
         <v>1093303735</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
@@ -11940,10 +11940,10 @@
         <v>1094054126</v>
       </c>
       <c r="D564" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E564" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11957,10 +11957,10 @@
         <v>1090388370</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -11974,10 +11974,10 @@
         <v>1092944823</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
@@ -11991,10 +11991,10 @@
         <v>1012377318</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -12008,10 +12008,10 @@
         <v>1091983085</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -12025,10 +12025,10 @@
         <v>1091362429</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
@@ -12042,10 +12042,10 @@
         <v>1127347554</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
@@ -12059,10 +12059,10 @@
         <v>1094832478</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -12076,10 +12076,10 @@
         <v>1092945853</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -12093,10 +12093,10 @@
         <v>1093298456</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
@@ -12110,10 +12110,10 @@
         <v>1127601987</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -12127,10 +12127,10 @@
         <v>1092947727</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -12144,10 +12144,10 @@
         <v>1093596340</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -12161,10 +12161,10 @@
         <v>5193779</v>
       </c>
       <c r="D577" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E577" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
@@ -12178,10 +12178,10 @@
         <v>1090435071</v>
       </c>
       <c r="D578" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E578" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
@@ -12195,7 +12195,7 @@
         <v>1093757866</v>
       </c>
       <c r="D579" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12209,7 +12209,7 @@
         <v>1092655252</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>

--- a/estudiantes.xlsx
+++ b/estudiantes.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unisimonedu-my.sharepoint.com/personal/wilson_castellanosv_unisimon_edu_co/Documents/2026/Del Colegio a Unisimón/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{771BCFF8-DBAE-49BF-B750-E72196680869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34277333-AC32-48AF-B211-02C3EDCA369A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{771BCFF8-DBAE-49BF-B750-E72196680869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A333D8D2-214F-4594-8FE7-3000A7C5295E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C6EF30D0-FF15-4CD4-92F1-E41695A57048}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$580</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="624">
   <si>
     <t>Nombre</t>
   </si>
@@ -1796,9 +1799,6 @@
     <t>Tarjeta de Identidad</t>
   </si>
   <si>
-    <t>Cédula de Ciudadania</t>
-  </si>
-  <si>
     <t>PPT</t>
   </si>
   <si>
@@ -1847,9 +1847,6 @@
     <t>Colegio Maria Goretti</t>
   </si>
   <si>
-    <t>Colegio Colegio Claudia Maria Prada</t>
-  </si>
-  <si>
     <t>Colegio Francisco José de Caldas</t>
   </si>
   <si>
@@ -1914,6 +1911,9 @@
   </si>
   <si>
     <t>Colegio Andres Bello</t>
+  </si>
+  <si>
+    <t>Cedula de Ciudadania</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +1980,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1997,7 +1997,14 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2357,6 +2364,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{370EFBFF-903A-44CE-9A7F-C89D3D1A4415}">
   <dimension ref="A1:E580"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="71" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2386,10 +2396,10 @@
         <v>1091976186</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2397,16 +2407,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C3" s="1">
+        <v>623</v>
+      </c>
+      <c r="C3" s="6">
         <v>1092534964</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2420,10 +2430,10 @@
         <v>1092537059</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2437,10 +2447,10 @@
         <v>1094052712</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2454,10 +2464,10 @@
         <v>1091979804</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2471,10 +2481,10 @@
         <v>1090437201</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2482,16 +2492,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C8" s="1">
+        <v>623</v>
+      </c>
+      <c r="C8" s="6">
         <v>1090385046</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2505,10 +2515,10 @@
         <v>1127658503</v>
       </c>
       <c r="D9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E9" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2522,10 +2532,10 @@
         <v>1092536878</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2533,16 +2543,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C11" s="1">
+        <v>623</v>
+      </c>
+      <c r="C11" s="6">
         <v>1092533900</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2556,10 +2566,10 @@
         <v>1094053556</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2567,16 +2577,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C13" s="1">
+        <v>623</v>
+      </c>
+      <c r="C13" s="6">
         <v>1090603719</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2590,10 +2600,10 @@
         <v>1094053187</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2607,10 +2617,10 @@
         <v>1016041526</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2624,10 +2634,10 @@
         <v>1092945020</v>
       </c>
       <c r="D16" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E16" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2641,10 +2651,10 @@
         <v>1091980752</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2658,10 +2668,10 @@
         <v>1092537874</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2675,10 +2685,10 @@
         <v>1093301679</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2692,10 +2702,10 @@
         <v>1091981605</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2709,10 +2719,10 @@
         <v>1092946078</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2726,10 +2736,10 @@
         <v>1091361112</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2737,16 +2747,16 @@
         <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C23" s="1">
         <v>6026735</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2754,16 +2764,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C24" s="1">
         <v>7704788</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2777,10 +2787,10 @@
         <v>1094053211</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2794,10 +2804,10 @@
         <v>1094053910</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2811,10 +2821,10 @@
         <v>1149465567</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2828,10 +2838,10 @@
         <v>1093599144</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2845,10 +2855,10 @@
         <v>1126424650</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2862,10 +2872,10 @@
         <v>1091976025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2879,10 +2889,10 @@
         <v>1025064345</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2890,16 +2900,16 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C32" s="1">
+        <v>623</v>
+      </c>
+      <c r="C32" s="6">
         <v>1091360424</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2913,10 +2923,10 @@
         <v>1090986975</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2924,16 +2934,16 @@
         <v>37</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C34" s="1">
+        <v>623</v>
+      </c>
+      <c r="C34" s="6">
         <v>1092343207</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2947,10 +2957,10 @@
         <v>1092945404</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2964,10 +2974,10 @@
         <v>1092946542</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2981,10 +2991,10 @@
         <v>1091978791</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2998,10 +3008,10 @@
         <v>1091976275</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3015,10 +3025,10 @@
         <v>1092947541</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3026,16 +3036,16 @@
         <v>43</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C40" s="1">
+        <v>623</v>
+      </c>
+      <c r="C40" s="6">
         <v>1090419598</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3049,10 +3059,10 @@
         <v>1127048335</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3066,10 +3076,10 @@
         <v>1092391604</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3083,10 +3093,10 @@
         <v>1093302640</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3094,16 +3104,16 @@
         <v>47</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C44" s="1">
+        <v>623</v>
+      </c>
+      <c r="C44" s="6">
         <v>1148954319</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3117,10 +3127,10 @@
         <v>1127360258</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3134,10 +3144,10 @@
         <v>1094055804</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3151,10 +3161,10 @@
         <v>1093301194</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3168,10 +3178,10 @@
         <v>1094052227</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3179,16 +3189,16 @@
         <v>52</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C49" s="1">
+        <v>623</v>
+      </c>
+      <c r="C49" s="6">
         <v>1030040974</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3202,10 +3212,10 @@
         <v>1092535898</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3213,16 +3223,16 @@
         <v>54</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C51" s="1">
+        <v>623</v>
+      </c>
+      <c r="C51" s="6">
         <v>1091974882</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3230,16 +3240,16 @@
         <v>55</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C52" s="1">
+        <v>623</v>
+      </c>
+      <c r="C52" s="6">
         <v>1090423988</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3253,10 +3263,10 @@
         <v>1091982241</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3270,10 +3280,10 @@
         <v>1092536353</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3287,10 +3297,10 @@
         <v>1064796517</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3304,10 +3314,10 @@
         <v>1127051841</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3321,10 +3331,10 @@
         <v>1092537856</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3338,10 +3348,10 @@
         <v>1092946382</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3355,10 +3365,10 @@
         <v>1091361943</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3372,10 +3382,10 @@
         <v>106290086664</v>
       </c>
       <c r="D60" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3389,10 +3399,10 @@
         <v>1091979127</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3406,10 +3416,10 @@
         <v>1092947321</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3423,10 +3433,10 @@
         <v>1065646657</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3440,10 +3450,10 @@
         <v>1094447499</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3457,10 +3467,10 @@
         <v>1091361489</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3474,10 +3484,10 @@
         <v>1092946733</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3491,10 +3501,10 @@
         <v>1093598851</v>
       </c>
       <c r="D67" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E67" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -3508,10 +3518,10 @@
         <v>1090439005</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3525,10 +3535,10 @@
         <v>1076507828</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3536,16 +3546,16 @@
         <v>73</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C70" s="1">
+        <v>623</v>
+      </c>
+      <c r="C70" s="6">
         <v>1094049337</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3559,10 +3569,10 @@
         <v>1093599248</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3576,10 +3586,10 @@
         <v>1093758488</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3593,10 +3603,10 @@
         <v>1091974878</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3610,10 +3620,10 @@
         <v>1110510788</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3627,10 +3637,10 @@
         <v>1091979213</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3644,10 +3654,10 @@
         <v>1093599162</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3661,10 +3671,10 @@
         <v>1093301646</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3672,16 +3682,16 @@
         <v>81</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C78" s="1">
+        <v>623</v>
+      </c>
+      <c r="C78" s="6">
         <v>1232593939</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3689,16 +3699,16 @@
         <v>82</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C79" s="1">
+        <v>623</v>
+      </c>
+      <c r="C79" s="6">
         <v>1094221476</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3712,10 +3722,10 @@
         <v>1093302031</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3729,10 +3739,10 @@
         <v>1091977878</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3746,10 +3756,10 @@
         <v>1091978811</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3763,10 +3773,10 @@
         <v>1093599780</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3780,10 +3790,10 @@
         <v>1092537114</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3797,10 +3807,10 @@
         <v>1093601080</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3814,10 +3824,10 @@
         <v>1094054137</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3831,10 +3841,10 @@
         <v>1091980194</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3848,10 +3858,10 @@
         <v>1092944759</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,10 +3875,10 @@
         <v>1093597850</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,10 +3892,10 @@
         <v>1029401766</v>
       </c>
       <c r="D90" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E90" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3899,10 +3909,10 @@
         <v>1093302625</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3910,16 +3920,16 @@
         <v>95</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C92" s="1">
         <v>5707410</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,16 +3937,16 @@
         <v>96</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C93" s="1">
         <v>1101340</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3944,16 +3954,16 @@
         <v>97</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C94" s="1">
+        <v>623</v>
+      </c>
+      <c r="C94" s="6">
         <v>1090520248</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3967,10 +3977,10 @@
         <v>1090434380</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3984,10 +3994,10 @@
         <v>1093598240</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -3995,16 +4005,16 @@
         <v>100</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C97" s="1">
+        <v>623</v>
+      </c>
+      <c r="C97" s="6">
         <v>1093595681</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4018,10 +4028,10 @@
         <v>1127358758</v>
       </c>
       <c r="D98" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E98" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4035,10 +4045,10 @@
         <v>1090431969</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4052,10 +4062,10 @@
         <v>1092945716</v>
       </c>
       <c r="D100" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E100" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4069,10 +4079,10 @@
         <v>1092947356</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4086,10 +4096,10 @@
         <v>1090474286</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4097,16 +4107,16 @@
         <v>106</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C103" s="1">
         <v>6152393</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4120,10 +4130,10 @@
         <v>1092388889</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4137,10 +4147,10 @@
         <v>1093300998</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4154,10 +4164,10 @@
         <v>1092946648</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4171,10 +4181,10 @@
         <v>1093600121</v>
       </c>
       <c r="D107" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E107" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4182,16 +4192,16 @@
         <v>111</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C108" s="1">
+        <v>623</v>
+      </c>
+      <c r="C108" s="6">
         <v>1094048621</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4205,10 +4215,10 @@
         <v>1093600765</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -4222,10 +4232,10 @@
         <v>1092945259</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -4239,10 +4249,10 @@
         <v>1092944636</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -4256,10 +4266,10 @@
         <v>1091362509</v>
       </c>
       <c r="D112" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -4273,10 +4283,10 @@
         <v>1091979298</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -4290,10 +4300,10 @@
         <v>1142718239</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -4301,16 +4311,16 @@
         <v>118</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C115" s="1">
+        <v>623</v>
+      </c>
+      <c r="C115" s="6">
         <v>1094051099</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -4324,10 +4334,10 @@
         <v>1092943899</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -4341,10 +4351,10 @@
         <v>1090426265</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -4352,16 +4362,16 @@
         <v>121</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C118" s="1">
         <v>5828829</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -4375,10 +4385,10 @@
         <v>1091981814</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -4392,10 +4402,10 @@
         <v>1094353336</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -4409,10 +4419,10 @@
         <v>1092946814</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -4426,10 +4436,10 @@
         <v>1091362734</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -4443,10 +4453,10 @@
         <v>1034782466</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -4460,10 +4470,10 @@
         <v>1183713018</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -4477,10 +4487,10 @@
         <v>1093597863</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -4494,10 +4504,10 @@
         <v>1030060516</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -4511,10 +4521,10 @@
         <v>1091362280</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -4528,10 +4538,10 @@
         <v>1091981450</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -4545,10 +4555,10 @@
         <v>1127345030</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -4562,10 +4572,10 @@
         <v>1094054384</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -4579,10 +4589,10 @@
         <v>1094222012</v>
       </c>
       <c r="D131" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -4596,10 +4606,10 @@
         <v>1093302655</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4613,10 +4623,10 @@
         <v>1093597855</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4630,10 +4640,10 @@
         <v>1094054415</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -4641,16 +4651,16 @@
         <v>138</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C135" s="1">
+        <v>623</v>
+      </c>
+      <c r="C135" s="6">
         <v>1093297176</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -4664,10 +4674,10 @@
         <v>1093599932</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4681,10 +4691,10 @@
         <v>1091978969</v>
       </c>
       <c r="D137" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E137" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -4698,10 +4708,10 @@
         <v>1091976475</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -4715,10 +4725,10 @@
         <v>1091982486</v>
       </c>
       <c r="D139" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E139" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -4732,10 +4742,10 @@
         <v>1093599623</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4743,16 +4753,16 @@
         <v>144</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C141" s="1">
+        <v>623</v>
+      </c>
+      <c r="C141" s="6">
         <v>1093298236</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4766,10 +4776,10 @@
         <v>1091981245</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4783,10 +4793,10 @@
         <v>1093598137</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -4800,10 +4810,10 @@
         <v>1093302496</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4817,10 +4827,10 @@
         <v>1090434688</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -4828,16 +4838,16 @@
         <v>149</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C146" s="1">
         <v>7662866</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -4851,10 +4861,10 @@
         <v>1091979906</v>
       </c>
       <c r="D147" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E147" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -4868,10 +4878,10 @@
         <v>1092946823</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4885,10 +4895,10 @@
         <v>1092946173</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -4896,16 +4906,16 @@
         <v>153</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C150" s="1">
         <v>5224194</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -4913,16 +4923,16 @@
         <v>154</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C151" s="1">
+        <v>623</v>
+      </c>
+      <c r="C151" s="6">
         <v>1093596931</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -4936,10 +4946,10 @@
         <v>1090509327</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -4953,10 +4963,10 @@
         <v>1092537531</v>
       </c>
       <c r="D153" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E153" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -4970,10 +4980,10 @@
         <v>1093600000</v>
       </c>
       <c r="D154" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E154" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -4987,10 +4997,10 @@
         <v>1140416716</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -5004,10 +5014,10 @@
         <v>1091981126</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -5021,10 +5031,10 @@
         <v>1090440910</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -5038,10 +5048,10 @@
         <v>1102364552</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -5055,10 +5065,10 @@
         <v>1091981235</v>
       </c>
       <c r="D159" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E159" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5072,10 +5082,10 @@
         <v>1093413049</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -5089,10 +5099,10 @@
         <v>1092536055</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5100,16 +5110,16 @@
         <v>165</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C162" s="5">
         <v>6770430</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -5123,10 +5133,10 @@
         <v>1091362054</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -5134,16 +5144,16 @@
         <v>167</v>
       </c>
       <c r="B164" t="s">
-        <v>585</v>
-      </c>
-      <c r="C164">
+        <v>623</v>
+      </c>
+      <c r="C164" s="7">
         <v>1092535094</v>
       </c>
       <c r="D164" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="E164" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5157,10 +5167,10 @@
         <v>1092537323</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -5168,16 +5178,16 @@
         <v>169</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C166" s="1">
+        <v>623</v>
+      </c>
+      <c r="C166" s="6">
         <v>1091974088</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -5191,10 +5201,10 @@
         <v>1091978107</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -5208,10 +5218,10 @@
         <v>1093599957</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -5225,10 +5235,10 @@
         <v>1091974916</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -5242,10 +5252,10 @@
         <v>1094221786</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -5259,10 +5269,10 @@
         <v>1091979182</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -5276,10 +5286,10 @@
         <v>1094055634</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -5293,10 +5303,10 @@
         <v>1091979479</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -5310,10 +5320,10 @@
         <v>1020765009</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -5327,10 +5337,10 @@
         <v>1127051197</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -5344,10 +5354,10 @@
         <v>1094054203</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -5355,16 +5365,16 @@
         <v>180</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C177" s="1">
         <v>5526781</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -5378,10 +5388,10 @@
         <v>1092946933</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -5389,16 +5399,16 @@
         <v>182</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C179" s="1">
         <v>5246648</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -5412,10 +5422,10 @@
         <v>1050611216</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -5429,10 +5439,10 @@
         <v>1127053174</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -5446,10 +5456,10 @@
         <v>1092537457</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -5463,10 +5473,10 @@
         <v>1091362218</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -5480,10 +5490,10 @@
         <v>1148217186</v>
       </c>
       <c r="D184" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E184" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -5491,16 +5501,16 @@
         <v>188</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C185" s="1">
         <v>1093760</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -5508,16 +5518,16 @@
         <v>189</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C186" s="1">
+        <v>623</v>
+      </c>
+      <c r="C186" s="6">
         <v>1245279053</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -5531,10 +5541,10 @@
         <v>1092945960</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -5548,10 +5558,10 @@
         <v>1094055408</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -5565,10 +5575,10 @@
         <v>1093302064</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -5582,10 +5592,10 @@
         <v>1092536311</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -5599,10 +5609,10 @@
         <v>1094348521</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -5616,10 +5626,10 @@
         <v>1092944323</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -5633,10 +5643,10 @@
         <v>1092945278</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -5644,16 +5654,16 @@
         <v>197</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C194" s="1">
         <v>5792510</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -5667,10 +5677,10 @@
         <v>1062908635</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -5684,10 +5694,10 @@
         <v>1091979775</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -5701,10 +5711,10 @@
         <v>1091980267</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -5718,10 +5728,10 @@
         <v>1127355375</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -5735,10 +5745,10 @@
         <v>1091979076</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -5752,10 +5762,10 @@
         <v>1091983269</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -5763,16 +5773,16 @@
         <v>204</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C201" s="1">
+        <v>623</v>
+      </c>
+      <c r="C201" s="6">
         <v>1092534996</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -5786,10 +5796,10 @@
         <v>1093301225</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -5803,10 +5813,10 @@
         <v>1093758076</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -5820,10 +5830,10 @@
         <v>1091979593</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -5837,10 +5847,10 @@
         <v>1091363313</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -5848,16 +5858,16 @@
         <v>209</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C206" s="1">
+        <v>623</v>
+      </c>
+      <c r="C206" s="6">
         <v>1090508661</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -5871,10 +5881,10 @@
         <v>1092946650</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -5882,16 +5892,16 @@
         <v>211</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C208" s="1">
         <v>6500648</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -5905,10 +5915,10 @@
         <v>1092538509</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -5922,10 +5932,10 @@
         <v>1093599971</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -5933,16 +5943,16 @@
         <v>214</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C211" s="1">
         <v>6815964</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -5950,16 +5960,16 @@
         <v>215</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C212" s="1">
+        <v>623</v>
+      </c>
+      <c r="C212" s="6">
         <v>1093752957</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -5973,10 +5983,10 @@
         <v>1092538360</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -5990,10 +6000,10 @@
         <v>1091361089</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6007,10 +6017,10 @@
         <v>1092947029</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6024,10 +6034,10 @@
         <v>1092945090</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6041,10 +6051,10 @@
         <v>1092945580</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -6058,10 +6068,10 @@
         <v>1090437625</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6069,16 +6079,16 @@
         <v>222</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C219" s="1">
+        <v>623</v>
+      </c>
+      <c r="C219" s="6">
         <v>1092342112</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -6086,16 +6096,16 @@
         <v>223</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C220" s="1">
+        <v>623</v>
+      </c>
+      <c r="C220" s="6">
         <v>1093753481</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6109,10 +6119,10 @@
         <v>1093600075</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6126,10 +6136,10 @@
         <v>1093598305</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6143,10 +6153,10 @@
         <v>1091980247</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6160,10 +6170,10 @@
         <v>1091361816</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6177,10 +6187,10 @@
         <v>1092537992</v>
       </c>
       <c r="D225" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E225" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6194,10 +6204,10 @@
         <v>1093301978</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6211,10 +6221,10 @@
         <v>1127946847</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6228,10 +6238,10 @@
         <v>1092535557</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6245,10 +6255,10 @@
         <v>1092536203</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6262,10 +6272,10 @@
         <v>1127050851</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6273,16 +6283,16 @@
         <v>234</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C231" s="1">
+        <v>623</v>
+      </c>
+      <c r="C231" s="6">
         <v>1082606446</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6296,10 +6306,10 @@
         <v>1094054318</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -6313,10 +6323,10 @@
         <v>1127357671</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6324,16 +6334,16 @@
         <v>237</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C234" s="1">
+        <v>623</v>
+      </c>
+      <c r="C234" s="6">
         <v>1091974909</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6347,10 +6357,10 @@
         <v>1091979846</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -6364,10 +6374,10 @@
         <v>1091978085</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -6381,10 +6391,10 @@
         <v>1014873678</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -6398,10 +6408,10 @@
         <v>1093300971</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -6415,10 +6425,10 @@
         <v>1093302270</v>
       </c>
       <c r="D239" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E239" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,10 +6442,10 @@
         <v>1140421305</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
@@ -6449,10 +6459,10 @@
         <v>1094054962</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -6466,10 +6476,10 @@
         <v>1125759472</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -6483,10 +6493,10 @@
         <v>1091980774</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -6500,10 +6510,10 @@
         <v>1092946963</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -6517,10 +6527,10 @@
         <v>1094053893</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -6534,10 +6544,10 @@
         <v>1094055412</v>
       </c>
       <c r="D246" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E246" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -6545,16 +6555,16 @@
         <v>250</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C247" s="1">
+        <v>623</v>
+      </c>
+      <c r="C247" s="6">
         <v>1090414848</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -6562,16 +6572,16 @@
         <v>251</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C248" s="1">
+        <v>623</v>
+      </c>
+      <c r="C248" s="6">
         <v>1093594703</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -6585,10 +6595,10 @@
         <v>1091978761</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -6596,16 +6606,16 @@
         <v>253</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C250" s="1">
+        <v>623</v>
+      </c>
+      <c r="C250" s="6">
         <v>1091975746</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -6619,10 +6629,10 @@
         <v>1091979536</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -6636,10 +6646,10 @@
         <v>1127945554</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -6653,10 +6663,10 @@
         <v>1148954130</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -6670,10 +6680,10 @@
         <v>1093615171</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
@@ -6687,10 +6697,10 @@
         <v>1093300387</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
@@ -6698,16 +6708,16 @@
         <v>259</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C256" s="1">
+        <v>623</v>
+      </c>
+      <c r="C256" s="6">
         <v>1092533137</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -6721,10 +6731,10 @@
         <v>1093802082</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -6738,10 +6748,10 @@
         <v>1093598785</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -6749,16 +6759,16 @@
         <v>262</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C259" s="1">
         <v>5464247</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -6766,16 +6776,16 @@
         <v>263</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C260" s="1">
+        <v>623</v>
+      </c>
+      <c r="C260" s="6">
         <v>1092966144</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -6789,10 +6799,10 @@
         <v>1091979801</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
@@ -6800,16 +6810,16 @@
         <v>265</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C262" s="1">
         <v>1256319</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -6823,10 +6833,10 @@
         <v>1093299754</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
@@ -6840,10 +6850,10 @@
         <v>1018441201</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -6857,10 +6867,10 @@
         <v>1093762955</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -6868,16 +6878,16 @@
         <v>269</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C266" s="1">
+        <v>623</v>
+      </c>
+      <c r="C266" s="6">
         <v>1091812275</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
@@ -6891,10 +6901,10 @@
         <v>1091362613</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -6902,16 +6912,16 @@
         <v>271</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C268" s="1">
+        <v>623</v>
+      </c>
+      <c r="C268" s="6">
         <v>1030060285</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -6925,10 +6935,10 @@
         <v>1091362761</v>
       </c>
       <c r="D269" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E269" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -6942,10 +6952,10 @@
         <v>1092946384</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
@@ -6953,16 +6963,16 @@
         <v>274</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C271" s="1">
         <v>1137719</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -6970,16 +6980,16 @@
         <v>275</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C272" s="1">
+        <v>623</v>
+      </c>
+      <c r="C272" s="6">
         <v>1127595940</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
@@ -6993,10 +7003,10 @@
         <v>1093598072</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
@@ -7010,10 +7020,10 @@
         <v>1091978513</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
@@ -7021,16 +7031,16 @@
         <v>278</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C275" s="1">
+        <v>623</v>
+      </c>
+      <c r="C275" s="6">
         <v>1092943381</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
@@ -7044,10 +7054,10 @@
         <v>1091980894</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
@@ -7061,10 +7071,10 @@
         <v>1092946012</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -7078,10 +7088,10 @@
         <v>1127347407</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
@@ -7095,10 +7105,10 @@
         <v>1094222262</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
@@ -7112,10 +7122,10 @@
         <v>1091978854</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -7129,10 +7139,10 @@
         <v>1094055100</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -7146,10 +7156,10 @@
         <v>1091980466</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
@@ -7163,10 +7173,10 @@
         <v>1092946757</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
@@ -7180,10 +7190,10 @@
         <v>1093309324</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
@@ -7197,10 +7207,10 @@
         <v>1091361992</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
@@ -7214,10 +7224,10 @@
         <v>1090449413</v>
       </c>
       <c r="D286" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E286" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -7231,10 +7241,10 @@
         <v>1092947203</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -7248,10 +7258,10 @@
         <v>1092538716</v>
       </c>
       <c r="D288" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E288" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -7265,10 +7275,10 @@
         <v>1094054354</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -7276,16 +7286,16 @@
         <v>293</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C290" s="1">
+        <v>623</v>
+      </c>
+      <c r="C290" s="6">
         <v>1094051540</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -7293,16 +7303,16 @@
         <v>294</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C291" s="1">
+        <v>623</v>
+      </c>
+      <c r="C291" s="6">
         <v>1090393154</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -7316,10 +7326,10 @@
         <v>1093599762</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -7327,16 +7337,16 @@
         <v>296</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C293" s="1">
+        <v>623</v>
+      </c>
+      <c r="C293" s="6">
         <v>1094051887</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -7350,10 +7360,10 @@
         <v>1094053741</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -7367,10 +7377,10 @@
         <v>1092944542</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -7384,10 +7394,10 @@
         <v>1030242123</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -7401,10 +7411,10 @@
         <v>1092947750</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -7412,16 +7422,16 @@
         <v>301</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C298" s="1">
         <v>7387500</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -7429,16 +7439,16 @@
         <v>302</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C299" s="1">
         <v>2385584</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -7452,10 +7462,10 @@
         <v>1091978076</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -7469,10 +7479,10 @@
         <v>1093600914</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -7486,10 +7496,10 @@
         <v>1091979862</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -7503,10 +7513,10 @@
         <v>1091981621</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -7520,10 +7530,10 @@
         <v>1091977941</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -7531,16 +7541,16 @@
         <v>308</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C305" s="1">
+        <v>623</v>
+      </c>
+      <c r="C305" s="6">
         <v>1030060353</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
@@ -7554,10 +7564,10 @@
         <v>1090440918</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -7571,10 +7581,10 @@
         <v>1091979331</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
@@ -7588,10 +7598,10 @@
         <v>1043677227</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -7605,10 +7615,10 @@
         <v>1148704495</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -7622,10 +7632,10 @@
         <v>1096952785</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
@@ -7639,10 +7649,10 @@
         <v>1092537741</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -7656,10 +7666,10 @@
         <v>1091980704</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -7673,10 +7683,10 @@
         <v>1091982629</v>
       </c>
       <c r="D313" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
@@ -7684,16 +7694,16 @@
         <v>317</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C314" s="1">
+        <v>623</v>
+      </c>
+      <c r="C314" s="6">
         <v>1091973415</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
@@ -7707,10 +7717,10 @@
         <v>1092536032</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
@@ -7718,16 +7728,16 @@
         <v>319</v>
       </c>
       <c r="B316" t="s">
-        <v>585</v>
-      </c>
-      <c r="C316">
+        <v>623</v>
+      </c>
+      <c r="C316" s="7">
         <v>1092538150</v>
       </c>
       <c r="D316" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
@@ -7735,16 +7745,16 @@
         <v>320</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C317" s="1">
+        <v>623</v>
+      </c>
+      <c r="C317" s="6">
         <v>1091391579</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
@@ -7758,10 +7768,10 @@
         <v>1090456843</v>
       </c>
       <c r="D318" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E318" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
@@ -7775,10 +7785,10 @@
         <v>1091361794</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
@@ -7792,10 +7802,10 @@
         <v>1093413084</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
@@ -7803,16 +7813,16 @@
         <v>324</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C321" s="1">
+        <v>623</v>
+      </c>
+      <c r="C321" s="6">
         <v>1094051318</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
@@ -7826,10 +7836,10 @@
         <v>1090450898</v>
       </c>
       <c r="D322" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E322" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
@@ -7843,10 +7853,10 @@
         <v>1030060502</v>
       </c>
       <c r="D323" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E323" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
@@ -7860,10 +7870,10 @@
         <v>1094055185</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -7877,10 +7887,10 @@
         <v>1091980319</v>
       </c>
       <c r="D325" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E325" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -7894,10 +7904,10 @@
         <v>1092538419</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
@@ -7911,10 +7921,10 @@
         <v>1092945955</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -7928,10 +7938,10 @@
         <v>1091982483</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -7945,10 +7955,10 @@
         <v>1091981256</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -7956,16 +7966,16 @@
         <v>333</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C330" s="1">
+        <v>623</v>
+      </c>
+      <c r="C330" s="6">
         <v>1093596535</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -7979,10 +7989,10 @@
         <v>1093597157</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -7996,10 +8006,10 @@
         <v>1127946279</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -8013,10 +8023,10 @@
         <v>1092535598</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -8030,10 +8040,10 @@
         <v>1091980526</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
@@ -8047,10 +8057,10 @@
         <v>1093301974</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
@@ -8064,10 +8074,10 @@
         <v>1092386675</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -8081,10 +8091,10 @@
         <v>1091978746</v>
       </c>
       <c r="D337" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E337" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -8098,10 +8108,10 @@
         <v>1093301950</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -8115,10 +8125,10 @@
         <v>1092388640</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
@@ -8132,10 +8142,10 @@
         <v>1090437202</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
@@ -8149,10 +8159,10 @@
         <v>1093758259</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -8166,10 +8176,10 @@
         <v>1090426977</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
@@ -8183,10 +8193,10 @@
         <v>1095839753</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
@@ -8200,10 +8210,10 @@
         <v>1093599888</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
@@ -8217,10 +8227,10 @@
         <v>1091362486</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -8234,10 +8244,10 @@
         <v>1093599404</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -8251,10 +8261,10 @@
         <v>1091361366</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -8268,10 +8278,10 @@
         <v>1091979718</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
@@ -8285,10 +8295,10 @@
         <v>1094054112</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
@@ -8296,16 +8306,16 @@
         <v>353</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C350" s="1">
+        <v>623</v>
+      </c>
+      <c r="C350" s="6">
         <v>1093594948</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -8319,10 +8329,10 @@
         <v>1092537274</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -8336,10 +8346,10 @@
         <v>1094055942</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -8353,10 +8363,10 @@
         <v>1091362593</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -8370,10 +8380,10 @@
         <v>1091970582</v>
       </c>
       <c r="D354" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -8387,10 +8397,10 @@
         <v>1091979582</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -8404,10 +8414,10 @@
         <v>1092946417</v>
       </c>
       <c r="D356" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
@@ -8421,10 +8431,10 @@
         <v>1092538132</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -8438,10 +8448,10 @@
         <v>1091977851</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -8455,10 +8465,10 @@
         <v>1091362123</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -8472,10 +8482,10 @@
         <v>1092537381</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
@@ -8489,10 +8499,10 @@
         <v>1091978266</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
@@ -8506,10 +8516,10 @@
         <v>1092536465</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -8523,10 +8533,10 @@
         <v>1148704011</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
@@ -8540,10 +8550,10 @@
         <v>1092946985</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
@@ -8557,10 +8567,10 @@
         <v>1127347347</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -8574,10 +8584,10 @@
         <v>1091372428</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -8591,10 +8601,10 @@
         <v>1094053345</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -8608,10 +8618,10 @@
         <v>1090434738</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -8625,10 +8635,10 @@
         <v>1093301726</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -8642,10 +8652,10 @@
         <v>1091979843</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -8659,10 +8669,10 @@
         <v>1091361246</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -8676,10 +8686,10 @@
         <v>1128225578</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -8693,10 +8703,10 @@
         <v>1093599432</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -8710,10 +8720,10 @@
         <v>1093599768</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -8721,16 +8731,16 @@
         <v>378</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C375" s="1">
         <v>5892051</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -8744,10 +8754,10 @@
         <v>1091980458</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -8761,10 +8771,10 @@
         <v>1091979100</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -8778,10 +8788,10 @@
         <v>1093300731</v>
       </c>
       <c r="D378" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
@@ -8789,16 +8799,16 @@
         <v>382</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C379" s="1">
         <v>6290709</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -8806,16 +8816,16 @@
         <v>383</v>
       </c>
       <c r="B380" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C380">
         <v>1091975808</v>
       </c>
       <c r="D380" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -8829,10 +8839,10 @@
         <v>1092947779</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -8846,10 +8856,10 @@
         <v>1092953076</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -8863,10 +8873,10 @@
         <v>1094054708</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
@@ -8880,10 +8890,10 @@
         <v>1092946710</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
@@ -8897,10 +8907,10 @@
         <v>1091979886</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -8914,10 +8924,10 @@
         <v>1093302431</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -8931,10 +8941,10 @@
         <v>1092947345</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -8948,10 +8958,10 @@
         <v>1091976732</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -8965,10 +8975,10 @@
         <v>1127658521</v>
       </c>
       <c r="D389" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E389" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -8976,16 +8986,16 @@
         <v>393</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C390" s="1">
+        <v>623</v>
+      </c>
+      <c r="C390" s="6">
         <v>1092534869</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -8999,10 +9009,10 @@
         <v>1092945615</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
@@ -9010,16 +9020,16 @@
         <v>395</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C392" s="1">
+        <v>623</v>
+      </c>
+      <c r="C392" s="6">
         <v>1094049486</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -9033,10 +9043,10 @@
         <v>1149457743</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
@@ -9050,10 +9060,10 @@
         <v>1127065536</v>
       </c>
       <c r="D394" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -9067,10 +9077,10 @@
         <v>1093598992</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
@@ -9078,16 +9088,16 @@
         <v>399</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C396" s="1">
+        <v>623</v>
+      </c>
+      <c r="C396" s="6">
         <v>1094367168</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -9101,10 +9111,10 @@
         <v>1092536345</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -9118,10 +9128,10 @@
         <v>1090425527</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
@@ -9135,10 +9145,10 @@
         <v>1092536717</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
@@ -9152,10 +9162,10 @@
         <v>1127049056</v>
       </c>
       <c r="D400" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E400" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
@@ -9169,10 +9179,10 @@
         <v>1091360739</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -9186,10 +9196,10 @@
         <v>1189963133</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
@@ -9203,10 +9213,10 @@
         <v>1030060548</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -9220,10 +9230,10 @@
         <v>1092946545</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
@@ -9231,16 +9241,16 @@
         <v>408</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C405" s="1">
         <v>5350012</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
@@ -9254,10 +9264,10 @@
         <v>1092538472</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
@@ -9271,10 +9281,10 @@
         <v>1091981708</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
@@ -9288,10 +9298,10 @@
         <v>1092945315</v>
       </c>
       <c r="D408" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E408" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
@@ -9305,10 +9315,10 @@
         <v>1148954031</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
@@ -9322,10 +9332,10 @@
         <v>1091976045</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
@@ -9339,10 +9349,10 @@
         <v>1049027222</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
@@ -9356,10 +9366,10 @@
         <v>1091360840</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -9373,10 +9383,10 @@
         <v>1091979496</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -9384,16 +9394,16 @@
         <v>417</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C414" s="1">
         <v>5251399</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
@@ -9407,10 +9417,10 @@
         <v>1090962777</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
@@ -9424,10 +9434,10 @@
         <v>1091979210</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -9441,10 +9451,10 @@
         <v>1093434411</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -9458,10 +9468,10 @@
         <v>1091978861</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -9475,10 +9485,10 @@
         <v>1091980875</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -9486,16 +9496,16 @@
         <v>423</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C420" s="1">
+        <v>623</v>
+      </c>
+      <c r="C420" s="6">
         <v>1094050953</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -9503,16 +9513,16 @@
         <v>424</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="C421" s="4">
+        <v>623</v>
+      </c>
+      <c r="C421" s="8">
         <v>1091974927</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -9526,10 +9536,10 @@
         <v>1093598343</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
@@ -9543,10 +9553,10 @@
         <v>1090537705</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -9560,10 +9570,10 @@
         <v>1127049539</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
@@ -9577,10 +9587,10 @@
         <v>1090448302</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
@@ -9594,10 +9604,10 @@
         <v>1094860586</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
@@ -9611,10 +9621,10 @@
         <v>1094053961</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
@@ -9622,16 +9632,16 @@
         <v>431</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C428" s="1">
+        <v>623</v>
+      </c>
+      <c r="C428" s="6">
         <v>1092534002</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
@@ -9645,10 +9655,10 @@
         <v>1092946702</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
@@ -9662,10 +9672,10 @@
         <v>1091998320</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
@@ -9673,16 +9683,16 @@
         <v>434</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C431" s="1">
+        <v>623</v>
+      </c>
+      <c r="C431" s="6">
         <v>1091980083</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
@@ -9696,10 +9706,10 @@
         <v>1093764881</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
@@ -9713,10 +9723,10 @@
         <v>1090433375</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
@@ -9730,10 +9740,10 @@
         <v>1127049000</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
@@ -9747,10 +9757,10 @@
         <v>1093597548</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -9764,10 +9774,10 @@
         <v>1093301671</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -9781,10 +9791,10 @@
         <v>1091979734</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
@@ -9792,16 +9802,16 @@
         <v>441</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="C438" s="4">
+        <v>623</v>
+      </c>
+      <c r="C438" s="8">
         <v>1091974658</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
@@ -9815,10 +9825,10 @@
         <v>1092947488</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
@@ -9832,10 +9842,10 @@
         <v>1091362929</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
@@ -9849,10 +9859,10 @@
         <v>1094054233</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
@@ -9866,10 +9876,10 @@
         <v>1091979877</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
@@ -9883,10 +9893,10 @@
         <v>1093301141</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
@@ -9900,10 +9910,10 @@
         <v>3170910390</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
@@ -9917,10 +9927,10 @@
         <v>1092537308</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
@@ -9934,10 +9944,10 @@
         <v>1091976004</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
@@ -9951,10 +9961,10 @@
         <v>1093301562</v>
       </c>
       <c r="D447" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -9968,10 +9978,10 @@
         <v>1091361827</v>
       </c>
       <c r="D448" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -9985,10 +9995,10 @@
         <v>1090435816</v>
       </c>
       <c r="D449" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E449" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
@@ -10002,10 +10012,10 @@
         <v>1091361484</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -10019,10 +10029,10 @@
         <v>1091980700</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -10036,10 +10046,10 @@
         <v>1091978598</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -10053,10 +10063,10 @@
         <v>1092947190</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
@@ -10070,10 +10080,10 @@
         <v>1091979808</v>
       </c>
       <c r="D454" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
@@ -10087,10 +10097,10 @@
         <v>1092538041</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -10104,10 +10114,10 @@
         <v>1092945903</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
@@ -10115,16 +10125,16 @@
         <v>460</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C457" s="6">
+        <v>623</v>
+      </c>
+      <c r="C457" s="9">
         <v>1091359878</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -10138,10 +10148,10 @@
         <v>1092536773</v>
       </c>
       <c r="D458" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E458" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
@@ -10149,16 +10159,16 @@
         <v>462</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C459" s="1">
+        <v>623</v>
+      </c>
+      <c r="C459" s="6">
         <v>1092534739</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
@@ -10166,16 +10176,16 @@
         <v>463</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C460" s="1">
+        <v>623</v>
+      </c>
+      <c r="C460" s="6">
         <v>1030060250</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
@@ -10189,10 +10199,10 @@
         <v>1093763001</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
@@ -10200,16 +10210,16 @@
         <v>465</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C462" s="1">
         <v>5227773</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
@@ -10217,16 +10227,16 @@
         <v>466</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C463" s="1">
+        <v>623</v>
+      </c>
+      <c r="C463" s="6">
         <v>1094051100</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
@@ -10240,10 +10250,10 @@
         <v>1092944562</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -10257,10 +10267,10 @@
         <v>1091977883</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
@@ -10274,10 +10284,10 @@
         <v>1094053614</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -10285,16 +10295,16 @@
         <v>470</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C467" s="1">
+        <v>623</v>
+      </c>
+      <c r="C467" s="6">
         <v>1093911533</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -10308,10 +10318,10 @@
         <v>1096953725</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
@@ -10325,10 +10335,10 @@
         <v>1091980516</v>
       </c>
       <c r="D469" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E469" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
@@ -10342,10 +10352,10 @@
         <v>1092537559</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -10359,10 +10369,10 @@
         <v>1094268662</v>
       </c>
       <c r="D471" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -10376,10 +10386,10 @@
         <v>1094054074</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
@@ -10393,10 +10403,10 @@
         <v>1091978337</v>
       </c>
       <c r="D473" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -10410,10 +10420,10 @@
         <v>1094054993</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -10427,10 +10437,10 @@
         <v>1093761308</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -10444,10 +10454,10 @@
         <v>1092944743</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
@@ -10455,16 +10465,16 @@
         <v>480</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C477" s="1">
+        <v>623</v>
+      </c>
+      <c r="C477" s="6">
         <v>1093298466</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
@@ -10478,10 +10488,10 @@
         <v>1091361907</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -10495,10 +10505,10 @@
         <v>1092947007</v>
       </c>
       <c r="D479" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -10512,10 +10522,10 @@
         <v>1093598245</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
@@ -10529,10 +10539,10 @@
         <v>1091976754</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
@@ -10546,10 +10556,10 @@
         <v>1092947395</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
@@ -10563,10 +10573,10 @@
         <v>1148954433</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
@@ -10580,10 +10590,10 @@
         <v>1092001118</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
@@ -10597,10 +10607,10 @@
         <v>1127349468</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
@@ -10614,10 +10624,10 @@
         <v>1093303479</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
@@ -10631,10 +10641,10 @@
         <v>1093600800</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
@@ -10648,10 +10658,10 @@
         <v>1092945676</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
@@ -10665,10 +10675,10 @@
         <v>1096245629</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
@@ -10682,10 +10692,10 @@
         <v>1092180722</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
@@ -10699,10 +10709,10 @@
         <v>1094222000</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -10716,10 +10726,10 @@
         <v>1092945317</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
@@ -10733,10 +10743,10 @@
         <v>1096804424</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
@@ -10750,10 +10760,10 @@
         <v>1030060307</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
@@ -10767,10 +10777,10 @@
         <v>1093911369</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
@@ -10784,10 +10794,10 @@
         <v>1094053970</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
@@ -10801,10 +10811,10 @@
         <v>1091980919</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
@@ -10818,10 +10828,10 @@
         <v>1093598479</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
@@ -10829,16 +10839,16 @@
         <v>502</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C499" s="1">
         <v>5107593</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
@@ -10852,10 +10862,10 @@
         <v>1091979602</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
@@ -10869,10 +10879,10 @@
         <v>1030041193</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
@@ -10886,10 +10896,10 @@
         <v>1092946181</v>
       </c>
       <c r="D502" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E502" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -10903,10 +10913,10 @@
         <v>1091979460</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
@@ -10920,10 +10930,10 @@
         <v>1090553680</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
@@ -10937,10 +10947,10 @@
         <v>1030060473</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -10954,10 +10964,10 @@
         <v>1091981186</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
@@ -10971,10 +10981,10 @@
         <v>1092945123</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
@@ -10982,16 +10992,16 @@
         <v>511</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C508" s="1">
+        <v>623</v>
+      </c>
+      <c r="C508" s="6">
         <v>1020744905</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
@@ -10999,16 +11009,16 @@
         <v>512</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C509" s="1">
+        <v>623</v>
+      </c>
+      <c r="C509" s="6">
         <v>1127347283</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
@@ -11022,10 +11032,10 @@
         <v>1013143334</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
@@ -11039,10 +11049,10 @@
         <v>1094054119</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
@@ -11056,10 +11066,10 @@
         <v>1094055437</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
@@ -11067,16 +11077,16 @@
         <v>516</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C513" s="1">
+        <v>623</v>
+      </c>
+      <c r="C513" s="6">
         <v>1094051566</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
@@ -11090,10 +11100,10 @@
         <v>1092536090</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
@@ -11107,10 +11117,10 @@
         <v>1094055491</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
@@ -11118,16 +11128,16 @@
         <v>519</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C516" s="1">
         <v>7358047</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
@@ -11141,10 +11151,10 @@
         <v>1091361820</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
@@ -11158,10 +11168,10 @@
         <v>1093599602</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
@@ -11175,10 +11185,10 @@
         <v>1090441662</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
@@ -11192,10 +11202,10 @@
         <v>1092537060</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
@@ -11209,10 +11219,10 @@
         <v>1092946087</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
@@ -11226,10 +11236,10 @@
         <v>1091981768</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
@@ -11237,16 +11247,16 @@
         <v>526</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C523" s="1">
+        <v>623</v>
+      </c>
+      <c r="C523" s="6">
         <v>1092943572</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E523" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
@@ -11260,10 +11270,10 @@
         <v>1092946550</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
@@ -11277,10 +11287,10 @@
         <v>1093300717</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
@@ -11294,10 +11304,10 @@
         <v>1093301806</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
@@ -11311,10 +11321,10 @@
         <v>1091979707</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -11328,10 +11338,10 @@
         <v>1091980057</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -11345,10 +11355,10 @@
         <v>1091806221</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E529" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
@@ -11362,10 +11372,10 @@
         <v>1092946639</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -11379,10 +11389,10 @@
         <v>1090520483</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -11396,10 +11406,10 @@
         <v>1091979929</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -11407,16 +11417,16 @@
         <v>536</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C533" s="1">
+        <v>623</v>
+      </c>
+      <c r="C533" s="6">
         <v>1030060343</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -11430,10 +11440,10 @@
         <v>1091977212</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -11441,16 +11451,16 @@
         <v>538</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C535" s="1">
         <v>1354249</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
@@ -11464,10 +11474,10 @@
         <v>1093597885</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
@@ -11475,16 +11485,16 @@
         <v>540</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C537" s="1">
+        <v>623</v>
+      </c>
+      <c r="C537" s="6">
         <v>1094348247</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -11498,10 +11508,10 @@
         <v>1091978375</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
@@ -11515,10 +11525,10 @@
         <v>1093302426</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
@@ -11532,10 +11542,10 @@
         <v>1093599059</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -11549,10 +11559,10 @@
         <v>1092536009</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -11566,10 +11576,10 @@
         <v>1092536054</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -11583,10 +11593,10 @@
         <v>1091369028</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -11600,10 +11610,10 @@
         <v>1091978877</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -11617,10 +11627,10 @@
         <v>1044632426</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -11634,10 +11644,10 @@
         <v>1127057409</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
@@ -11651,10 +11661,10 @@
         <v>1091976301</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
@@ -11668,10 +11678,10 @@
         <v>1093301947</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
@@ -11679,16 +11689,16 @@
         <v>552</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C549" s="1">
+        <v>623</v>
+      </c>
+      <c r="C549" s="6">
         <v>1093596673</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -11702,10 +11712,10 @@
         <v>1092943507</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
@@ -11719,10 +11729,10 @@
         <v>1091979559</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
@@ -11736,10 +11746,10 @@
         <v>1091361582</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
@@ -11747,16 +11757,16 @@
         <v>556</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C553" s="1">
+        <v>623</v>
+      </c>
+      <c r="C553" s="6">
         <v>1091974981</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -11770,10 +11780,10 @@
         <v>1091362282</v>
       </c>
       <c r="D554" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E554" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
@@ -11787,10 +11797,10 @@
         <v>1090439668</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
@@ -11804,10 +11814,10 @@
         <v>1094053554</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -11821,10 +11831,10 @@
         <v>1091975810</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -11838,10 +11848,10 @@
         <v>1092537908</v>
       </c>
       <c r="D558" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E558" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
@@ -11855,10 +11865,10 @@
         <v>1090449366</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
@@ -11872,10 +11882,10 @@
         <v>1157963048</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -11889,10 +11899,10 @@
         <v>1064996939</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
@@ -11906,10 +11916,10 @@
         <v>1093413083</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
@@ -11923,10 +11933,10 @@
         <v>1093303735</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
@@ -11934,16 +11944,16 @@
         <v>567</v>
       </c>
       <c r="B564" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C564">
         <v>1094054126</v>
       </c>
       <c r="D564" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E564" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -11957,10 +11967,10 @@
         <v>1090388370</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
@@ -11974,10 +11984,10 @@
         <v>1092944823</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
@@ -11991,10 +12001,10 @@
         <v>1012377318</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -12008,10 +12018,10 @@
         <v>1091983085</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -12025,10 +12035,10 @@
         <v>1091362429</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
@@ -12042,10 +12052,10 @@
         <v>1127347554</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
@@ -12059,10 +12069,10 @@
         <v>1094832478</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -12076,10 +12086,10 @@
         <v>1092945853</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -12087,16 +12097,16 @@
         <v>576</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C573" s="1">
+        <v>623</v>
+      </c>
+      <c r="C573" s="6">
         <v>1093298456</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
@@ -12110,10 +12120,10 @@
         <v>1127601987</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -12127,10 +12137,10 @@
         <v>1092947727</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -12138,16 +12148,16 @@
         <v>579</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C576" s="1">
+        <v>623</v>
+      </c>
+      <c r="C576" s="6">
         <v>1093596340</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -12155,16 +12165,16 @@
         <v>580</v>
       </c>
       <c r="B577" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C577">
         <v>5193779</v>
       </c>
       <c r="D577" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E577" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
@@ -12178,10 +12188,10 @@
         <v>1090435071</v>
       </c>
       <c r="D578" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E578" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
@@ -12195,7 +12205,7 @@
         <v>1093757866</v>
       </c>
       <c r="D579" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -12203,16 +12213,17 @@
         <v>583</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="C580" s="1">
+        <v>623</v>
+      </c>
+      <c r="C580" s="6">
         <v>1092655252</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E580" xr:uid="{370EFBFF-903A-44CE-9A7F-C89D3D1A4415}"/>
   <conditionalFormatting sqref="C2:C580">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
